--- a/data/trans_bre/IP04D$individual-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Habitat-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 3,23</t>
+          <t>-13,61; 4,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 17,28</t>
+          <t>-1,25; 17,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,1; -0,4</t>
+          <t>-31,89; -0,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-41,0; 13,22</t>
+          <t>-39,8; 17,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 87,96</t>
+          <t>-4,72; 90,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-69,64; -1,1</t>
+          <t>-73,11; -3,11</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 7,43</t>
+          <t>-6,11; 7,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 8,33</t>
+          <t>-6,18; 7,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 4,59</t>
+          <t>-8,6; 4,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 31,12</t>
+          <t>-19,66; 31,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 33,37</t>
+          <t>-18,36; 29,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 30,5</t>
+          <t>-40,11; 33,23</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 2,72</t>
+          <t>-12,18; 2,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 10,06</t>
+          <t>-6,87; 10,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,8; -2,96</t>
+          <t>-15,77; -3,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 12,23</t>
+          <t>-39,99; 13,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 34,52</t>
+          <t>-18,44; 36,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-85,53; -26,75</t>
+          <t>-87,04; -33,95</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 1,45</t>
+          <t>-14,3; 1,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 10,87</t>
+          <t>-5,1; 10,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 11,1</t>
+          <t>-6,23; 11,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 3,89</t>
+          <t>-30,87; 5,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 46,19</t>
+          <t>-16,42; 44,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 51,5</t>
+          <t>-19,73; 48,98</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 0,53</t>
+          <t>-7,22; 0,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,94</t>
+          <t>-0,53; 7,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -0,92</t>
+          <t>-9,54; -0,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 1,52</t>
+          <t>-21,44; 1,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 25,45</t>
+          <t>-1,79; 27,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,39; -4,53</t>
+          <t>-40,27; -2,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Habitat-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 4,12</t>
+          <t>-13,57; 4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 17,05</t>
+          <t>-2,03; 16,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,89; -0,71</t>
+          <t>-28,3; -0,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 17,44</t>
+          <t>-40,5; 18,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 90,62</t>
+          <t>-7,05; 84,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-73,11; -3,11</t>
+          <t>-67,61; 0,48</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 7,44</t>
+          <t>-6,11; 7,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 7,9</t>
+          <t>-5,01; 8,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 4,86</t>
+          <t>-8,87; 4,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 31,07</t>
+          <t>-19,71; 29,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 29,56</t>
+          <t>-15,16; 29,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 33,23</t>
+          <t>-41,75; 31,05</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 2,56</t>
+          <t>-12,0; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 10,75</t>
+          <t>-6,32; 9,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -3,25</t>
+          <t>-16,01; -3,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 13,02</t>
+          <t>-40,06; 11,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 36,01</t>
+          <t>-16,81; 34,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-87,04; -33,95</t>
+          <t>-86,29; -28,51</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 1,9</t>
+          <t>-14,22; 1,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 10,23</t>
+          <t>-4,37; 10,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 11,15</t>
+          <t>-5,47; 11,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 5,34</t>
+          <t>-30,93; 5,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 44,99</t>
+          <t>-13,87; 44,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 48,98</t>
+          <t>-17,88; 51,59</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,51</t>
+          <t>-7,34; 0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 7,31</t>
+          <t>-0,98; 6,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -0,54</t>
+          <t>-9,07; 0,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 1,72</t>
+          <t>-21,84; 3,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 27,57</t>
+          <t>-3,48; 25,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,27; -2,88</t>
+          <t>-38,81; 0,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Habitat-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-11,08</t>
+          <t>-11,65</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-38,71%</t>
+          <t>-40,5%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 4,65</t>
+          <t>-14,39; 3,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 16,62</t>
+          <t>-1,93; 17,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,3; -0,2</t>
+          <t>-27,86; -1,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 18,2</t>
+          <t>-41,0; 13,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 84,12</t>
+          <t>-7,36; 87,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,61; 0,48</t>
+          <t>-66,78; -2,87</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,92</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,78%</t>
+          <t>-2,99%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 7,39</t>
+          <t>-6,53; 7,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 8,02</t>
+          <t>-6,22; 8,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 4,5</t>
+          <t>-7,54; 6,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 29,7</t>
+          <t>-19,91; 31,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 29,67</t>
+          <t>-18,38; 33,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 31,05</t>
+          <t>-36,64; 41,35</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-8,13</t>
+          <t>-8,2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-66,8%</t>
+          <t>-63,94%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 2,66</t>
+          <t>-12,41; 2,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 9,9</t>
+          <t>-6,06; 10,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -3,0</t>
+          <t>-15,32; -2,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-40,06; 11,38</t>
+          <t>-41,97; 12,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 34,46</t>
+          <t>-16,49; 34,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-86,29; -28,51</t>
+          <t>-83,15; -21,11</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 1,66</t>
+          <t>-14,39; 1,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 10,29</t>
+          <t>-3,71; 10,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 11,18</t>
+          <t>-7,35; 10,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 5,64</t>
+          <t>-31,38; 3,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 44,23</t>
+          <t>-12,59; 46,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 51,59</t>
+          <t>-23,65; 44,68</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,41</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-21,44%</t>
+          <t>-17,41%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 0,97</t>
+          <t>-7,06; 0,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 6,79</t>
+          <t>-1,04; 6,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,12</t>
+          <t>-8,0; 0,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 3,23</t>
+          <t>-21,49; 1,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 25,5</t>
+          <t>-3,73; 25,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,81; 0,71</t>
+          <t>-34,2; 1,44</t>
         </is>
       </c>
     </row>
